--- a/docs/产线配方.xlsx
+++ b/docs/产线配方.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepos\endfield_blueprint_tool\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepos\endfield_blueprint_tool\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{368031F5-B51F-4956-AD55-45628B25CC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F3653D5-BAF3-41D8-A180-E458BAD1884F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2157,7 +2157,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>31</v>
+        <v>120</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>91</v>
